--- a/task146/golden/ic_preview_2026-10-10.xlsx
+++ b/task146/golden/ic_preview_2026-10-10.xlsx
@@ -629,7 +629,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>11687</v>
+        <v>11695</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -642,7 +642,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="3">
-        <v>40524</v>
+        <v>30182</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -650,7 +650,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="5">
-        <v>39.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -901,13 +901,13 @@
         <v>33</v>
       </c>
       <c r="B5" s="3">
-        <v>7139</v>
+        <v>7096</v>
       </c>
       <c r="C5" s="3">
-        <v>7381</v>
+        <v>7353</v>
       </c>
       <c r="D5" s="5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -915,13 +915,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="3">
-        <v>3788</v>
+        <v>3751</v>
       </c>
       <c r="C6" s="3">
-        <v>3738</v>
+        <v>3799</v>
       </c>
       <c r="D6" s="5">
-        <v>-1.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -929,13 +929,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="3">
-        <v>22083</v>
+        <v>21906</v>
       </c>
       <c r="C7" s="3">
-        <v>20806</v>
+        <v>20858</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.8</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -943,13 +943,13 @@
         <v>36</v>
       </c>
       <c r="B8" s="3">
-        <v>22163</v>
+        <v>21899</v>
       </c>
       <c r="C8" s="3">
-        <v>34354</v>
+        <v>34794</v>
       </c>
       <c r="D8" s="5">
-        <v>55</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -957,13 +957,13 @@
         <v>37</v>
       </c>
       <c r="B9" s="3">
-        <v>15624</v>
+        <v>15444</v>
       </c>
       <c r="C9" s="3">
-        <v>15387</v>
+        <v>15565</v>
       </c>
       <c r="D9" s="5">
-        <v>-1.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -971,13 +971,13 @@
         <v>38</v>
       </c>
       <c r="B10" s="3">
-        <v>15563</v>
+        <v>15630</v>
       </c>
       <c r="C10" s="3">
-        <v>15935</v>
+        <v>15801</v>
       </c>
       <c r="D10" s="5">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -985,13 +985,13 @@
         <v>39</v>
       </c>
       <c r="B11" s="3">
-        <v>17559</v>
+        <v>17623</v>
       </c>
       <c r="C11" s="3">
-        <v>21331</v>
+        <v>21427</v>
       </c>
       <c r="D11" s="5">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -999,13 +999,13 @@
         <v>40</v>
       </c>
       <c r="B12" s="3">
-        <v>5028</v>
+        <v>5130</v>
       </c>
       <c r="C12" s="3">
-        <v>4506</v>
+        <v>4524</v>
       </c>
       <c r="D12" s="5">
-        <v>-10.4</v>
+        <v>-11.8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1013,13 +1013,13 @@
         <v>41</v>
       </c>
       <c r="B13" s="3">
-        <v>5883</v>
+        <v>5865</v>
       </c>
       <c r="C13" s="3">
-        <v>5319</v>
+        <v>5454</v>
       </c>
       <c r="D13" s="5">
-        <v>-9.6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1027,13 +1027,13 @@
         <v>42</v>
       </c>
       <c r="B14" s="3">
-        <v>7643</v>
+        <v>7404</v>
       </c>
       <c r="C14" s="3">
-        <v>7183</v>
+        <v>7227</v>
       </c>
       <c r="D14" s="5">
-        <v>-6</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1041,13 +1041,13 @@
         <v>43</v>
       </c>
       <c r="B15" s="3">
-        <v>12081</v>
+        <v>11876</v>
       </c>
       <c r="C15" s="3">
-        <v>11813</v>
+        <v>12032</v>
       </c>
       <c r="D15" s="5">
-        <v>-2.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1055,13 +1055,13 @@
         <v>44</v>
       </c>
       <c r="B16" s="3">
-        <v>4089</v>
+        <v>4095</v>
       </c>
       <c r="C16" s="3">
-        <v>4060</v>
+        <v>4053</v>
       </c>
       <c r="D16" s="5">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1069,13 +1069,13 @@
         <v>45</v>
       </c>
       <c r="B17" s="3">
-        <v>4651</v>
+        <v>4753</v>
       </c>
       <c r="C17" s="3">
-        <v>4759</v>
+        <v>4885</v>
       </c>
       <c r="D17" s="5">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1083,13 +1083,13 @@
         <v>46</v>
       </c>
       <c r="B18" s="3">
-        <v>13425</v>
+        <v>13466</v>
       </c>
       <c r="C18" s="3">
-        <v>12751</v>
+        <v>12779</v>
       </c>
       <c r="D18" s="5">
-        <v>-5</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1097,13 +1097,13 @@
         <v>47</v>
       </c>
       <c r="B19" s="10">
-        <v>156719</v>
+        <v>155938</v>
       </c>
       <c r="C19" s="10">
-        <v>169323</v>
+        <v>170551</v>
       </c>
       <c r="D19" s="11">
-        <v>8</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>

--- a/task146/golden/ic_preview_2026-10-10.xlsx
+++ b/task146/golden/ic_preview_2026-10-10.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Initial claims preview, claims week ended 10 October 2026</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">  of which Western, Coastal and Island (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">  of which Western, Coastal and Island, made in September (%)</t>
+  </si>
+  <si>
     <t>Claims expected to be filed again in the week, low</t>
   </si>
   <si>
@@ -61,7 +64,7 @@
     <t>The rest of the week, high</t>
   </si>
   <si>
-    <t>Each region's July to September determinations at the share its own first claims weeks of a quarter have filed again since 2014; about four fifths of the claims filed again are in Western, Coastal and Island.</t>
+    <t>Each region's July, August and September determinations, month by month, at the shares its own first claims weeks of a quarter have filed again since 2014; about nine tenths of the claims filed again are in Western, Coastal and Island.</t>
   </si>
   <si>
     <t>Workers to be laid off under layoff notices given to the board, by region of the site and month of the first layoff</t>
@@ -599,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A054BD3-0CA3-5D5A-B473-77AF429E572E}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84.7109375" customWidth="1"/>
@@ -621,7 +624,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>16000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -629,7 +632,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <v>11695</v>
+        <v>11814</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -642,7 +645,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="3">
-        <v>30182</v>
+        <v>26035</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -650,15 +653,15 @@
         <v>6</v>
       </c>
       <c r="B9" s="5">
-        <v>48.5</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="3">
-        <v>4000</v>
+      <c r="B10" s="5">
+        <v>55.3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -674,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>11000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -682,12 +685,20 @@
         <v>10</v>
       </c>
       <c r="B13" s="3">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>11</v>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -708,31 +719,31 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3">
         <v>111</v>
@@ -746,7 +757,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3">
         <v>360</v>
@@ -760,7 +771,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3">
         <v>205</v>
@@ -774,7 +785,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3">
         <v>198</v>
@@ -788,7 +799,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3">
         <v>198</v>
@@ -802,7 +813,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3">
         <v>136</v>
@@ -816,7 +827,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3">
         <v>300</v>
@@ -830,7 +841,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3">
         <v>350</v>
@@ -844,7 +855,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="10">
         <v>1858</v>
@@ -874,236 +885,236 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
-        <v>7096</v>
+        <v>7094</v>
       </c>
       <c r="C5" s="3">
-        <v>7353</v>
+        <v>7554</v>
       </c>
       <c r="D5" s="5">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
-        <v>3751</v>
+        <v>3725</v>
       </c>
       <c r="C6" s="3">
-        <v>3799</v>
+        <v>3759</v>
       </c>
       <c r="D6" s="5">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="3">
-        <v>21906</v>
+        <v>22193</v>
       </c>
       <c r="C7" s="3">
-        <v>20858</v>
+        <v>21265</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.8</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
-        <v>21899</v>
+        <v>22080</v>
       </c>
       <c r="C8" s="3">
-        <v>34794</v>
+        <v>35395</v>
       </c>
       <c r="D8" s="5">
-        <v>58.9</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3">
-        <v>15444</v>
+        <v>15150</v>
       </c>
       <c r="C9" s="3">
-        <v>15565</v>
+        <v>15818</v>
       </c>
       <c r="D9" s="5">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3">
-        <v>15630</v>
+        <v>15482</v>
       </c>
       <c r="C10" s="3">
-        <v>15801</v>
+        <v>16114</v>
       </c>
       <c r="D10" s="5">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="3">
-        <v>17623</v>
+        <v>17544</v>
       </c>
       <c r="C11" s="3">
-        <v>21427</v>
+        <v>22120</v>
       </c>
       <c r="D11" s="5">
-        <v>21.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="3">
-        <v>5130</v>
+        <v>5124</v>
       </c>
       <c r="C12" s="3">
         <v>4524</v>
       </c>
       <c r="D12" s="5">
-        <v>-11.8</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="3">
-        <v>5865</v>
+        <v>5565</v>
       </c>
       <c r="C13" s="3">
-        <v>5454</v>
+        <v>5497</v>
       </c>
       <c r="D13" s="5">
-        <v>-7</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="3">
-        <v>7404</v>
+        <v>7585</v>
       </c>
       <c r="C14" s="3">
-        <v>7227</v>
+        <v>7108</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.4</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="3">
-        <v>11876</v>
+        <v>11963</v>
       </c>
       <c r="C15" s="3">
-        <v>12032</v>
+        <v>12237</v>
       </c>
       <c r="D15" s="5">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="3">
-        <v>4095</v>
+        <v>3960</v>
       </c>
       <c r="C16" s="3">
-        <v>4053</v>
+        <v>4226</v>
       </c>
       <c r="D16" s="5">
-        <v>-1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="3">
-        <v>4753</v>
+        <v>4676</v>
       </c>
       <c r="C17" s="3">
-        <v>4885</v>
+        <v>4905</v>
       </c>
       <c r="D17" s="5">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="3">
-        <v>13466</v>
+        <v>13386</v>
       </c>
       <c r="C18" s="3">
-        <v>12779</v>
+        <v>13022</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.1</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="10">
-        <v>155938</v>
+        <v>155527</v>
       </c>
       <c r="C19" s="10">
-        <v>170551</v>
+        <v>173544</v>
       </c>
       <c r="D19" s="11">
-        <v>9.4</v>
+        <v>11.6</v>
       </c>
     </row>
   </sheetData>
@@ -1122,50 +1133,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
